--- a/ExcelUpload/students_data.xlsx
+++ b/ExcelUpload/students_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Vegaahi\CFM-1\ExcelUpload\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{28F75176-E361-4485-B8FF-AA88726F146F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE2DB057-CC4A-4D48-8708-A112D320DED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="221">
   <si>
     <t>htnumber</t>
   </si>
@@ -607,20 +607,100 @@
     <t>ADM015</t>
   </si>
   <si>
-    <t>2024-06-24</t>
-  </si>
-  <si>
-    <t>2003-07-21</t>
+    <t>HT016</t>
+  </si>
+  <si>
+    <t>bhavana</t>
+  </si>
+  <si>
+    <t>Venkanna</t>
+  </si>
+  <si>
+    <t>street1</t>
+  </si>
+  <si>
+    <t>bhavana@gmail.com</t>
+  </si>
+  <si>
+    <t>BC_D</t>
+  </si>
+  <si>
+    <t>ADM016</t>
+  </si>
+  <si>
+    <t>HT017</t>
+  </si>
+  <si>
+    <t>HT018</t>
+  </si>
+  <si>
+    <t>HT019</t>
+  </si>
+  <si>
+    <t>HT020</t>
+  </si>
+  <si>
+    <t>HT021</t>
+  </si>
+  <si>
+    <t>ADM017</t>
+  </si>
+  <si>
+    <t>ADM018</t>
+  </si>
+  <si>
+    <t>ADM019</t>
+  </si>
+  <si>
+    <t>ADM020</t>
+  </si>
+  <si>
+    <t>ADM021</t>
+  </si>
+  <si>
+    <t>bhavana1@gmail.com</t>
+  </si>
+  <si>
+    <t>bhavana3@gmail.com</t>
+  </si>
+  <si>
+    <t>bhavana4@gmail.com</t>
+  </si>
+  <si>
+    <t>bhavana5@gmail.com</t>
+  </si>
+  <si>
+    <t>bhavana6@gmail.com</t>
+  </si>
+  <si>
+    <t>HT022</t>
+  </si>
+  <si>
+    <t>HT023</t>
+  </si>
+  <si>
+    <t>ADM022</t>
+  </si>
+  <si>
+    <t>ADM023</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -643,13 +723,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -950,8 +1034,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:R24"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="5" max="6" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.6328125" customWidth="1"/>
+    <col min="9" max="9" width="28.453125" customWidth="1"/>
+    <col min="14" max="15" width="10.08984375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
@@ -1833,11 +1923,11 @@
       <c r="M16" t="s">
         <v>194</v>
       </c>
-      <c r="N16" t="s">
-        <v>195</v>
-      </c>
-      <c r="O16" t="s">
-        <v>196</v>
+      <c r="N16" s="2">
+        <v>45467</v>
+      </c>
+      <c r="O16" s="2">
+        <v>37823</v>
       </c>
       <c r="P16">
         <v>42000</v>
@@ -1849,7 +1939,465 @@
         <v>6900</v>
       </c>
     </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>195</v>
+      </c>
+      <c r="B17" t="s">
+        <v>196</v>
+      </c>
+      <c r="C17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" t="s">
+        <v>197</v>
+      </c>
+      <c r="E17">
+        <v>1234567891</v>
+      </c>
+      <c r="F17">
+        <v>1234567892</v>
+      </c>
+      <c r="G17" t="s">
+        <v>198</v>
+      </c>
+      <c r="H17">
+        <v>123456789034</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="J17" t="s">
+        <v>27</v>
+      </c>
+      <c r="K17" t="s">
+        <v>200</v>
+      </c>
+      <c r="L17" t="s">
+        <v>44</v>
+      </c>
+      <c r="M17" t="s">
+        <v>201</v>
+      </c>
+      <c r="N17" s="2">
+        <v>45467</v>
+      </c>
+      <c r="O17" s="2">
+        <v>37823</v>
+      </c>
+      <c r="P17">
+        <v>42000</v>
+      </c>
+      <c r="Q17">
+        <v>5000</v>
+      </c>
+      <c r="R17">
+        <v>6900</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>202</v>
+      </c>
+      <c r="B18" t="s">
+        <v>196</v>
+      </c>
+      <c r="C18" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" t="s">
+        <v>197</v>
+      </c>
+      <c r="E18">
+        <v>1234567893</v>
+      </c>
+      <c r="F18">
+        <v>1234567892</v>
+      </c>
+      <c r="G18" t="s">
+        <v>198</v>
+      </c>
+      <c r="H18">
+        <v>123456789545</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="J18" t="s">
+        <v>27</v>
+      </c>
+      <c r="K18" t="s">
+        <v>200</v>
+      </c>
+      <c r="L18" t="s">
+        <v>44</v>
+      </c>
+      <c r="M18" t="s">
+        <v>207</v>
+      </c>
+      <c r="N18" s="2">
+        <v>45467</v>
+      </c>
+      <c r="O18" s="2">
+        <v>37823</v>
+      </c>
+      <c r="P18">
+        <v>42000</v>
+      </c>
+      <c r="Q18">
+        <v>5000</v>
+      </c>
+      <c r="R18">
+        <v>6900</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>203</v>
+      </c>
+      <c r="B19" t="s">
+        <v>196</v>
+      </c>
+      <c r="C19" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19" t="s">
+        <v>197</v>
+      </c>
+      <c r="E19">
+        <v>1234567898</v>
+      </c>
+      <c r="F19">
+        <v>1234567872</v>
+      </c>
+      <c r="G19" t="s">
+        <v>198</v>
+      </c>
+      <c r="H19">
+        <v>123456789542</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="J19" t="s">
+        <v>27</v>
+      </c>
+      <c r="K19" t="s">
+        <v>200</v>
+      </c>
+      <c r="L19" t="s">
+        <v>44</v>
+      </c>
+      <c r="M19" t="s">
+        <v>208</v>
+      </c>
+      <c r="N19" s="2">
+        <v>45467</v>
+      </c>
+      <c r="O19" s="2">
+        <v>37823</v>
+      </c>
+      <c r="P19">
+        <v>42000</v>
+      </c>
+      <c r="Q19">
+        <v>5000</v>
+      </c>
+      <c r="R19">
+        <v>6900</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>204</v>
+      </c>
+      <c r="B20" t="s">
+        <v>196</v>
+      </c>
+      <c r="C20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" t="s">
+        <v>197</v>
+      </c>
+      <c r="E20">
+        <v>1234567890</v>
+      </c>
+      <c r="F20">
+        <v>1234567897</v>
+      </c>
+      <c r="G20" t="s">
+        <v>198</v>
+      </c>
+      <c r="H20">
+        <v>123456789562</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="J20" t="s">
+        <v>27</v>
+      </c>
+      <c r="K20" t="s">
+        <v>200</v>
+      </c>
+      <c r="L20" t="s">
+        <v>44</v>
+      </c>
+      <c r="M20" t="s">
+        <v>209</v>
+      </c>
+      <c r="N20" s="2">
+        <v>45467</v>
+      </c>
+      <c r="O20" s="2">
+        <v>37823</v>
+      </c>
+      <c r="P20">
+        <v>42000</v>
+      </c>
+      <c r="Q20">
+        <v>5000</v>
+      </c>
+      <c r="R20">
+        <v>6900</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>205</v>
+      </c>
+      <c r="B21" t="s">
+        <v>196</v>
+      </c>
+      <c r="C21" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" t="s">
+        <v>197</v>
+      </c>
+      <c r="E21">
+        <v>1234567892</v>
+      </c>
+      <c r="F21">
+        <v>1234567882</v>
+      </c>
+      <c r="G21" t="s">
+        <v>198</v>
+      </c>
+      <c r="H21">
+        <v>123456789942</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="J21" t="s">
+        <v>27</v>
+      </c>
+      <c r="K21" t="s">
+        <v>200</v>
+      </c>
+      <c r="L21" t="s">
+        <v>44</v>
+      </c>
+      <c r="M21" t="s">
+        <v>210</v>
+      </c>
+      <c r="N21" s="2">
+        <v>45467</v>
+      </c>
+      <c r="O21" s="2">
+        <v>37823</v>
+      </c>
+      <c r="P21">
+        <v>42000</v>
+      </c>
+      <c r="Q21">
+        <v>5000</v>
+      </c>
+      <c r="R21">
+        <v>6900</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>206</v>
+      </c>
+      <c r="B22" t="s">
+        <v>196</v>
+      </c>
+      <c r="C22" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" t="s">
+        <v>197</v>
+      </c>
+      <c r="E22">
+        <v>1234567897</v>
+      </c>
+      <c r="F22">
+        <v>1234567852</v>
+      </c>
+      <c r="G22" t="s">
+        <v>198</v>
+      </c>
+      <c r="H22">
+        <v>123456781542</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="J22" t="s">
+        <v>27</v>
+      </c>
+      <c r="K22" t="s">
+        <v>200</v>
+      </c>
+      <c r="L22" t="s">
+        <v>44</v>
+      </c>
+      <c r="M22" t="s">
+        <v>211</v>
+      </c>
+      <c r="N22" s="2">
+        <v>45467</v>
+      </c>
+      <c r="O22" s="2">
+        <v>37823</v>
+      </c>
+      <c r="P22">
+        <v>42000</v>
+      </c>
+      <c r="Q22">
+        <v>5000</v>
+      </c>
+      <c r="R22">
+        <v>6900</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>217</v>
+      </c>
+      <c r="B23" t="s">
+        <v>196</v>
+      </c>
+      <c r="C23" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" t="s">
+        <v>197</v>
+      </c>
+      <c r="E23">
+        <v>1234567887</v>
+      </c>
+      <c r="F23">
+        <v>1234567552</v>
+      </c>
+      <c r="G23" t="s">
+        <v>198</v>
+      </c>
+      <c r="H23">
+        <v>123956781542</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="J23" t="s">
+        <v>27</v>
+      </c>
+      <c r="K23" t="s">
+        <v>200</v>
+      </c>
+      <c r="L23" t="s">
+        <v>44</v>
+      </c>
+      <c r="M23" t="s">
+        <v>219</v>
+      </c>
+      <c r="N23" s="2">
+        <v>45467</v>
+      </c>
+      <c r="O23" s="2">
+        <v>37823</v>
+      </c>
+      <c r="P23">
+        <v>42000</v>
+      </c>
+      <c r="Q23">
+        <v>5000</v>
+      </c>
+      <c r="R23">
+        <v>6900</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>218</v>
+      </c>
+      <c r="B24" t="s">
+        <v>196</v>
+      </c>
+      <c r="C24" t="s">
+        <v>20</v>
+      </c>
+      <c r="D24" t="s">
+        <v>197</v>
+      </c>
+      <c r="E24">
+        <v>1234567807</v>
+      </c>
+      <c r="F24">
+        <v>1234561852</v>
+      </c>
+      <c r="G24" t="s">
+        <v>198</v>
+      </c>
+      <c r="H24">
+        <v>125456781542</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="J24" t="s">
+        <v>27</v>
+      </c>
+      <c r="K24" t="s">
+        <v>200</v>
+      </c>
+      <c r="L24" t="s">
+        <v>44</v>
+      </c>
+      <c r="M24" t="s">
+        <v>220</v>
+      </c>
+      <c r="N24" s="2">
+        <v>45467</v>
+      </c>
+      <c r="O24" s="2">
+        <v>37823</v>
+      </c>
+      <c r="P24">
+        <v>42000</v>
+      </c>
+      <c r="Q24">
+        <v>5000</v>
+      </c>
+      <c r="R24">
+        <v>6900</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="I17" r:id="rId1" xr:uid="{7ED85757-E7A8-4F28-B33E-97924D0AE500}"/>
+    <hyperlink ref="I18" r:id="rId2" xr:uid="{6BF03927-582C-4942-B313-B807DEF9A782}"/>
+    <hyperlink ref="I19" r:id="rId3" xr:uid="{5B080E39-72BC-42A8-A2FA-DCA7517F63F7}"/>
+    <hyperlink ref="I20" r:id="rId4" xr:uid="{ED780F28-C7A2-44B5-8CA0-3369A4CDAD1F}"/>
+    <hyperlink ref="I21" r:id="rId5" xr:uid="{4F7CAC21-C671-41A9-97E9-0B9323AF7CAA}"/>
+    <hyperlink ref="I22" r:id="rId6" xr:uid="{BAB69B04-D40F-477D-B612-96EE505C6621}"/>
+    <hyperlink ref="I23" r:id="rId7" xr:uid="{3C3E8B9D-C852-46F5-BA22-04D047D8F384}"/>
+    <hyperlink ref="I24" r:id="rId8" xr:uid="{BCB698A6-8183-4EDD-B603-37B79275A365}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>